--- a/daily_matches/job_matches_2026-10-01.xlsx
+++ b/daily_matches/job_matches_2026-10-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CIM GROUP</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.7</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, CatBoost, Azure ML, Data Lake, MLflow</t>
+          <t>Data Scientist, RAG, XGBoost, CatBoost, BigQuery, Docker, Kubernetes, Apache Airflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,94 +496,94 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1dc346effcd7bb8</t>
+          <t>https://www.indeed.com/viewjob?jk=e93507bcf9f653a6</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Python Developer-6</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.3</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Gemini, FAISS, Pinecone, ChromaDB, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f0b13030305a263</t>
+          <t>https://www.indeed.com/viewjob?jk=b53e345da3563756</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Slalom Flex (Project-Based) - Data Engineer</t>
+          <t>Sr. Automation Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Zifo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Redshift, BigQuery, MLflow, CI/CD, Terraform, Snowflake, Databricks, BigQuery</t>
+          <t>TensorFlow, PyTorch, S3, EC2, FastAPI, Docker, Apache Airflow, CI/CD, Git, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b4726a6ec8ee51c</t>
+          <t>https://www.indeed.com/viewjob?jk=cb99ce16f3e25727</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Zeitview</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,42 +591,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, BigQuery, FastAPI, CI/CD, Snowflake, BigQuery</t>
+          <t>RAG, Copilot, S3, EC2, Docker, CI/CD, Git, Kafka, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620b02de3a55862c</t>
+          <t>https://www.indeed.com/viewjob?jk=bece6dc9082488c8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Threat Intelligence</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Proofpoint</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, EC2, FastAPI, Docker, AKS, CI/CD, GitHub Actions, Git, PostgreSQL, Python</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3c8c0c1096d1374</t>
+          <t>https://www.indeed.com/viewjob?jk=5eab9d45a7707f9c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist, 2027 Graduate U.S.</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Atlassian</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Prompt Engineering, BigQuery, Snowflake, Databricks, BigQuery, Tableau, Matplotlib, Python, SQL</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc9c7878ada8fc3</t>
+          <t>https://www.indeed.com/viewjob?jk=0ab75b27388163f6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Maple Grove, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=192ac4a678cf384e</t>
+          <t>https://www.indeed.com/viewjob?jk=cd9f207b6755f4c7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Azure Data Engineer Senior</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>AmeriHealth Caritas</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, PyTorch, MLflow, Docker, Jenkins, Git</t>
+          <t>Data Scientist, RAG, Prompt Engineering, Data Lake, CI/CD, Git, Snowflake, Databricks, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707fe6b50d7f37de</t>
+          <t>https://www.indeed.com/viewjob?jk=fc8b1810e1fdd4c8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Applied Scientist Intern</t>
+          <t>Software Engineer – SaaS &amp; Data Migration Specialist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Solen Software Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Python, SQL</t>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c9c1e47d3b71c6</t>
+          <t>https://www.indeed.com/viewjob?jk=1e93b4193751c0db</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Generative AI Engineer / QA Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, BigQuery, CI/CD, Snowflake, BigQuery, Hadoop</t>
+          <t>RAG, Redshift, BigQuery, Data Lake, Git, Snowflake, BigQuery, Redshift, Kafka, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3abf2400e71f03</t>
+          <t>https://www.indeed.com/viewjob?jk=f98b7445f4c23e54</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, PyTorch, MLflow, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb50ef2eb953b805</t>
+          <t>https://www.indeed.com/viewjob?jk=b1e24ff3eadd50fe</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Full Stack .Net Developer</t>
+          <t>Senior AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Starr Companies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, Docker, Kubernetes, CI/CD, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce193f64bbb24a65</t>
+          <t>https://www.indeed.com/viewjob?jk=a364ae5a19b7869c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Powerplatform Developer</t>
+          <t>AI Engineer / Forward Deployed Engineer (AI Engineering)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Data Lake, Dataflow, CI/CD, Git, Python, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9817ad9b58fb2bb</t>
+          <t>https://www.indeed.com/viewjob?jk=596f2c1f457b5aff</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Kubernetes, CI/CD, Jenkins, Terraform, Git, Power BI, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb98f02f8244206</t>
+          <t>https://www.indeed.com/viewjob?jk=fb19bd4ef6a4ada2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Toshiba Global Commerce Solutions</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a77ce8eb404fca8</t>
+          <t>https://www.indeed.com/viewjob?jk=7a0f122e9187f4e1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Toshiba Global Commerce Solutions</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38d32f4e2e1b8b14</t>
+          <t>https://www.indeed.com/viewjob?jk=0d07c3bb23686820</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Toshiba Global Commerce Solutions</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59f8aec47e006c03</t>
+          <t>https://www.indeed.com/viewjob?jk=211b0a055f958ee2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Full-Stack Engineer 5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Toshiba Global Commerce Solutions</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=153bd394afeacd39</t>
+          <t>https://www.indeed.com/viewjob?jk=64b2e71c99f69dd6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer III - Developer Productivity</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, MongoDB, NoSQL, Python, SQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ae76a9628628c7</t>
+          <t>https://www.indeed.com/viewjob?jk=0bdd28ae23a357c1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Powerplatform Developer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Data Lake, Dataflow, CI/CD, Git, Python, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43a4a1045fc06fa5</t>
+          <t>https://www.indeed.com/viewjob?jk=2d06a6189a87b46f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dynatrace Platform Engineer</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RHONDOS</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, SQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66919fdddcdfcb04</t>
+          <t>https://www.indeed.com/viewjob?jk=2cc840015b470f1d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI and Analytics Specialist</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Prompt Engineering, Cortex, Snowflake, Tableau, Power BI, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2921ad09c5da181</t>
+          <t>https://www.indeed.com/viewjob?jk=544fd4c8961f1ea1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI and Analytics Specialist</t>
+          <t>Full-stack Engineer 4, Agentic Orchestration</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Prompt Engineering, Cortex, Snowflake, Tableau, Power BI, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d01c676ad477e9</t>
+          <t>https://www.indeed.com/viewjob?jk=e32202cd85d558d0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vida Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f62682570ca4564</t>
+          <t>https://www.indeed.com/viewjob?jk=7d2c8d56a4de6d75</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AI Agent Platform</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, LLaMA, Gemini, Kubernetes, CI/CD, Kafka, Python, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73139f978d2dee4b</t>
+          <t>https://www.indeed.com/viewjob?jk=a8711133b275b7eb</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AI Agent Platform</t>
+          <t>Full-stack Engineer 4 (Python, Typescript, React, AWS)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, LLaMA, Gemini, Kubernetes, CI/CD, Kafka, Python, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7e910ae68cda876</t>
+          <t>https://www.indeed.com/viewjob?jk=a1054d75a23b6d7e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AI Agent Platform</t>
+          <t>Full Stack Engineer 4 (Global Payment Network)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, LLaMA, Gemini, Kubernetes, CI/CD, Kafka, Python, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=317afb6e1c196afc</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb953856e305a64</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Engineer Internship</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kaizen Analytix LLC</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Git, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c1131aca69bd715</t>
+          <t>https://www.indeed.com/viewjob?jk=2e7b649fedb1b1f4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>.Net Architect</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,15 +1458,15 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, AKS, CI/CD, Git, Power BI, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, Kubernetes, CI/CD, Jenkins, Terraform, Git, Power BI, Python</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bdb8fdc819fc93</t>
+          <t>https://www.indeed.com/viewjob?jk=d01528e1099d2199</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Systems Development Engineer I</t>
+          <t>Senior Engineer - Machine Learning</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc08aecc58d44c7</t>
+          <t>https://www.indeed.com/viewjob?jk=531655aaad41cc6b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>.Net Architect</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, AKS, CI/CD, Git, Power BI, SQL, R</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8857d4686b086ade</t>
+          <t>https://www.indeed.com/viewjob?jk=57fc7c51cc89d701</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Business Analytics Engineer</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Orange EV</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Creve Coeur, MO, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Synapse, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b11b2a8e2e0c14</t>
+          <t>https://www.indeed.com/viewjob?jk=ca37fe7a7b840de0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Innovation</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Sidley Austin</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Davidson, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, Docker, Kubernetes, CI/CD, Git, PostgreSQL, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3600504cf03f63ae</t>
+          <t>https://www.indeed.com/viewjob?jk=eba421b036375606</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer, Engineering Applications</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CMG Financial</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+          <t>Copilot, FastAPI, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9112581e70dc489f</t>
+          <t>https://www.indeed.com/viewjob?jk=0f46dbaea5d78f85</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID)</t>
+          <t>Senior Data Analyst - Department of Human Services</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>C-4 Analytics</t>
+          <t>El Paso County, CO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, MongoDB, Python, SQL, R, Java, Scala</t>
+          <t>RAG, BigQuery, Git, Snowflake, BigQuery, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,137 +1686,137 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8dddb0f6933d4b5</t>
+          <t>https://www.indeed.com/viewjob?jk=253da0fe6fe5ed62</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Platform Infrastructure</t>
+          <t>Internship, Data Engineer, Data Engineering &amp; Business Intelligence (Winter/Spring2027)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cricut</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, EC2, Kinesis, Terraform, Git, R, Scala</t>
+          <t>RAG, Prompt Engineering, FastAPI, Apache Airflow, PostgreSQL, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25f7cd8749b833c</t>
+          <t>https://www.indeed.com/viewjob?jk=b91b59fb02bdf0b4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Consultant - Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Torq</t>
+          <t>Gallup</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+          <t>S3, CI/CD, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c3401d941824e0d</t>
+          <t>https://www.indeed.com/viewjob?jk=85f30de6c0e5da73</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Consultant - Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Torq</t>
+          <t>MarLabs</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+          <t>RAG, Synapse, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ac82b7a6d54f881</t>
+          <t>https://www.indeed.com/viewjob?jk=de102d1cdc393b78</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Consultant - Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Torq</t>
+          <t>First Bank</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+          <t>Generative AI, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Kafka, R, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64e067b6a9457a6</t>
+          <t>https://www.indeed.com/viewjob?jk=87565d685b23a868</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Consultant - Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Torq</t>
+          <t>First Bank</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+          <t>Generative AI, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Kafka, R, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d8fd9e2003203af</t>
+          <t>https://www.indeed.com/viewjob?jk=19069c3d35411178</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Consultant - Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Torq</t>
+          <t>First Bank</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+          <t>Generative AI, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Kafka, R, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a078ee8f3e015f</t>
+          <t>https://www.indeed.com/viewjob?jk=c9703405ee731b3b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Snr. Site Reliability Engineer (Remote)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>KnowBe4</t>
+          <t>First Bank</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Wilmington, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>Generative AI, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Kafka, R, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5cb08dca80f82f</t>
+          <t>https://www.indeed.com/viewjob?jk=56aea2a70012464c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>foureyes</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RAG, Dataflow, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, A/B Testing</t>
+          <t>Copilot, S3, Terraform, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac16ebb3b7d3a45</t>
+          <t>https://www.indeed.com/viewjob?jk=129e88ac4f26e5cc</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Experienced QA Professional with AI Skills</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bethpage, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RAG, Dataflow, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, A/B Testing</t>
+          <t>RAG, Copilot, Prompt Engineering, NLTK, CI/CD, Jenkins, Git, Python, R</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d08c7ede9b3f07e5</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa138fec881740a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Engineer, Site Reliability</t>
+          <t>Data Science Research Internship</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>IDeaS</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Generative AI, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, Python, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,322 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a034f54de3b89a97</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Senior Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Adonis</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0454d0d787afaef</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Wipro</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03a0022898c8e203</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Application Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Cadre5</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d844e003c06f439</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Full-Stack</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Curai Health</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>RAG, FastAPI, Docker, Terraform, Git, NoSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=30bc150668d4c229</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Software Development Engineer II</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Yardi Systems</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Oxnard, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, PostgreSQL, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4d3a314b3c5b198a</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, AI Authoring</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Unity Technologies</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Mountain View, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, R, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e605c01b7232d436</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>First Bank</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Generative AI, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Kafka, R, Scala</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=55d0379462176349</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>EOS IT Solutions</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Generative AI, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1581b1cc29413e</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Data Scientist Senior Associate</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, Git, Tableau, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db3f1da0759efe9e</t>
+          <t>https://www.indeed.com/viewjob?jk=1ad0f4c7b4326a1b</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-10-01.xlsx
+++ b/daily_matches/job_matches_2026-10-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior GenAI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, CatBoost, BigQuery, Docker, Kubernetes, Apache Airflow, CI/CD, Jenkins</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93507bcf9f653a6</t>
+          <t>https://www.indeed.com/viewjob?jk=6d49e93ee840c19e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior GenAI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,34 +521,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b53e345da3563756</t>
+          <t>https://www.indeed.com/viewjob?jk=9980838379e7321e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Automation Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Zifo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, S3, EC2, FastAPI, Docker, Apache Airflow, CI/CD, Git, NoSQL</t>
+          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb99ce16f3e25727</t>
+          <t>https://www.indeed.com/viewjob?jk=d567bfdb83525baa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Data Science Supervisor</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zeitview</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Docker, CI/CD, Git, Kafka, PostgreSQL, Python</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Keras, BigQuery, Dataflow, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bece6dc9082488c8</t>
+          <t>https://www.indeed.com/viewjob?jk=3b26def0f0e58209</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Pillsbury Winthrop Shaw Pittman</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,252 +626,252 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>AI Engineer, RAG, Data Lake, GitHub Actions, Terraform, Git, Databricks, PySpark, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eab9d45a7707f9c</t>
+          <t>https://www.indeed.com/viewjob?jk=d4506845d5307539</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>AI Agent Engineer, AMS Automation</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Saarthee</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>RAG, Gemini, Pinecone, FastAPI, Docker, Kubernetes, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ab75b27388163f6</t>
+          <t>https://www.indeed.com/viewjob?jk=45e4646cba97e893</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>FCCI Insurance Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>RAG, CI/CD, Git, Databricks, PySpark, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd9f207b6755f4c7</t>
+          <t>https://www.indeed.com/viewjob?jk=0cf8e2097b223c45</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Azure Data Engineer Senior</t>
+          <t>Senior Software Engineer, Reporting</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AmeriHealth Caritas</t>
+          <t>JustPark</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Data Lake, CI/CD, Git, Snowflake, Databricks, PySpark, Kafka</t>
+          <t>RAG, Copilot, S3, BigQuery, Kinesis, Kubernetes, CI/CD, GitHub Actions, Git, BigQuery</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc8b1810e1fdd4c8</t>
+          <t>https://www.indeed.com/viewjob?jk=d9067ce361a1da61</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer – SaaS &amp; Data Migration Specialist</t>
+          <t>Agentic AI Developer III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Solen Software Group</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e93b4193751c0db</t>
+          <t>https://www.indeed.com/viewjob?jk=ea2f608016c3b6e2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Engineer III - Platform Application Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>A-V SERVICES INC.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Data Lake, Git, Snowflake, BigQuery, Redshift, Kafka, SQL</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f98b7445f4c23e54</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9985441c9238ec</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Freshfields</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, PyTorch, MLflow, Docker, Jenkins, Git</t>
+          <t>RAG, Docker, AKS, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1e24ff3eadd50fe</t>
+          <t>https://www.indeed.com/viewjob?jk=d9d12e8cbf2f5bba</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AI Full Stack Engineer</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, LLaMA, Docker, Kubernetes, CI/CD, Git, Databricks, Python</t>
+          <t>Docker, Kubernetes, CI/CD, Git, Kafka, MongoDB, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a364ae5a19b7869c</t>
+          <t>https://www.indeed.com/viewjob?jk=c372fec6954adf93</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Engineer / Forward Deployed Engineer (AI Engineering)</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Vestmark</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, CI/CD, Git, Python, R</t>
+          <t>AI Engineer, Prompt Engineering, PostgreSQL, MySQL, MongoDB, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,159 +916,159 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596f2c1f457b5aff</t>
+          <t>https://www.indeed.com/viewjob?jk=3c6a5e5cf5e67a8d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Support Engineer (TeamCity)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JetBrains</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb19bd4ef6a4ada2</t>
+          <t>https://www.indeed.com/viewjob?jk=5921dacde6ad5818</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Product Engineer, Associate</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Pacific Gas and Electric</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Copilot, CI/CD, Terraform, Git, PostgreSQL, MySQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a0f122e9187f4e1</t>
+          <t>https://www.indeed.com/viewjob?jk=1dacfdc0a247a93d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Pillsbury Winthrop Shaw Pittman</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, RAG, MLflow, Databricks, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d07c3bb23686820</t>
+          <t>https://www.indeed.com/viewjob?jk=17e50e0275d56546</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>AI and Software Solutions Architect (Remote, Contract)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>INFUSE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Kubernetes, AKS, Kafka, PostgreSQL, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211b0a055f958ee2</t>
+          <t>https://www.indeed.com/viewjob?jk=b1bfa1f3245af737</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 5</t>
+          <t>Software Engineer III - ML Model Delivery</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1077,103 +1077,103 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, S3, Docker, Kubernetes, Terraform, Databricks, Python, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b2e71c99f69dd6</t>
+          <t>https://www.indeed.com/viewjob?jk=a9623715fec95146</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Legal Solutions Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Freshfields</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Docker, AKS, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bdd28ae23a357c1</t>
+          <t>https://www.indeed.com/viewjob?jk=a78a626370aa6018</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Consultant - Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Torq Consulting</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d06a6189a87b46f</t>
+          <t>https://www.indeed.com/viewjob?jk=87462cba5b348ed2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Senior Consultant - Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Torq Consulting</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1182,116 +1182,116 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cc840015b470f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbe099f28678d2b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>GRP Solutions</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544fd4c8961f1ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=0b9fce73a2238a5b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4, Agentic Orchestration</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Pillsbury Winthrop Shaw Pittman</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, RAG, MLflow, Databricks, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e32202cd85d558d0</t>
+          <t>https://www.indeed.com/viewjob?jk=1cd3548c5f4e148d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>New College Grad - Industrial Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Manassas, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, Git, Tableau, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d2c8d56a4de6d75</t>
+          <t>https://www.indeed.com/viewjob?jk=edfb8807e4ec3a5f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Universal Background Screening</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Docker, Kubernetes, CI/CD, Git, MySQL, MongoDB, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8711133b275b7eb</t>
+          <t>https://www.indeed.com/viewjob?jk=1802ad0b463648dd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Python, Typescript, React, AWS)</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Copilot, S3, CI/CD, Terraform, Git, SQL, R, Java</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,672 +1371,77 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1054d75a23b6d7e</t>
+          <t>https://www.indeed.com/viewjob?jk=fea647a8765adb1b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (Global Payment Network)</t>
+          <t>Senior Enterprise Data Modeler</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>BOK Financial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Data Lake, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb953856e305a64</t>
+          <t>https://www.indeed.com/viewjob?jk=699494cdcc6e8afe</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Software Engineer - Contact Center</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Macy's</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>Johns Creek, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Kafka, Hadoop, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e7b649fedb1b1f4</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Kubernetes, CI/CD, Jenkins, Terraform, Git, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d01528e1099d2199</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Machine Learning</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Qualcomm</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=531655aaad41cc6b</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Qualcomm</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57fc7c51cc89d701</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Orange EV</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Kansas City, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Synapse, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Databricks, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca37fe7a7b840de0</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Sidley Austin</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>AI Engineer, Docker, Kubernetes, CI/CD, Git, PostgreSQL, NoSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eba421b036375606</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer, Engineering Applications</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Rivian</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Copilot, FastAPI, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f46dbaea5d78f85</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst - Department of Human Services</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>El Paso County, CO</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Colorado Springs, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Git, Snowflake, BigQuery, Power BI, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=253da0fe6fe5ed62</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Internship, Data Engineer, Data Engineering &amp; Business Intelligence (Winter/Spring2027)</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Tesla</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Fremont, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, FastAPI, Apache Airflow, PostgreSQL, MySQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b91b59fb02bdf0b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Gallup</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>S3, CI/CD, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=85f30de6c0e5da73</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>MarLabs</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>RAG, Synapse, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=de102d1cdc393b78</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>First Bank</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Generative AI, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Kafka, R, Scala</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87565d685b23a868</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>First Bank</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Greensboro, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Generative AI, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Kafka, R, Scala</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=19069c3d35411178</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>First Bank</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Generative AI, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Kafka, R, Scala</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c9703405ee731b3b</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>First Bank</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Wilmington, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Generative AI, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Kafka, R, Scala</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56aea2a70012464c</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>foureyes</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Copilot, S3, Terraform, Git, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=129e88ac4f26e5cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Experienced QA Professional with AI Skills</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, NLTK, CI/CD, Jenkins, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa138fec881740a</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Data Science Research Internship</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>IDeaS</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Bloomington, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1ad0f4c7b4326a1b</t>
+          <t>https://www.indeed.com/viewjob?jk=accfe7542b4f2229</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-10-01.xlsx
+++ b/daily_matches/job_matches_2026-10-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior GenAI Engineer</t>
+          <t>AWS Lakehouse Data Engineer- GrantSolutions experienced only</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Triwave Solutions Inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,11 +482,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>26.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes</t>
+          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, Kinesis, Docker, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d49e93ee840c19e</t>
+          <t>https://www.indeed.com/viewjob?jk=16509765dca147b7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior GenAI Engineer</t>
+          <t>Financial Services Technology Consulting, Financial Risk Technology (FRT) Engineering - Senior</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>23.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes</t>
+          <t>LangChain, RAG, S3, EC2, Data Lake, Docker, Kubernetes, AKS, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9980838379e7321e</t>
+          <t>https://www.indeed.com/viewjob?jk=8d4e445d09c33470</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Sr. Clinical Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>Copilot, Redshift, BigQuery, Synapse, CI/CD, Git, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d567bfdb83525baa</t>
+          <t>https://www.indeed.com/viewjob?jk=17f0d739bf16af91</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Science Supervisor</t>
+          <t>Shelton - Data Engineering - Engr- Data II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Keras, BigQuery, Dataflow, Docker, CI/CD</t>
+          <t>RAG, Cortex, S3, Glue, Kinesis, CI/CD, Git, Snowflake, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b26def0f0e58209</t>
+          <t>https://www.indeed.com/viewjob?jk=92ef615c91382283</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>AI Engineer (Data Scientist)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pillsbury Winthrop Shaw Pittman</t>
+          <t>Zions Bancorporation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Data Lake, GitHub Actions, Terraform, Git, Databricks, PySpark, PostgreSQL, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, PyTorch, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4506845d5307539</t>
+          <t>https://www.indeed.com/viewjob?jk=d1815eb45aa2c108</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Agent Engineer, AMS Automation</t>
+          <t>Data Architect - Associate</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Saarthee</t>
+          <t>Intermountain Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>West Valley City, UT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Pinecone, FastAPI, Docker, Kubernetes, CI/CD, Git, Python, SQL</t>
+          <t>RAG, Kinesis, CI/CD, Snowflake, Databricks, PySpark, Kafka, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e4646cba97e893</t>
+          <t>https://www.indeed.com/viewjob?jk=8052dec6a7c72b4e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FCCI Insurance Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Databricks, PySpark, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, Apache Airflow, CI/CD, GitHub Actions, Git, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cf8e2097b223c45</t>
+          <t>https://www.indeed.com/viewjob?jk=24dadced559e6fd5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Reporting</t>
+          <t>Full Stack Engineer 4 (Python, Java, AWS)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JustPark</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, BigQuery, Kinesis, Kubernetes, CI/CD, GitHub Actions, Git, BigQuery</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9067ce361a1da61</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa0a61b0b1456bb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Agentic AI Developer III</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea2f608016c3b6e2</t>
+          <t>https://www.indeed.com/viewjob?jk=3c87481ab8ef4260</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer III - Platform Application Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A-V SERVICES INC.</t>
+          <t>NOV</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R</t>
+          <t>Data Scientist, Data Lake, CI/CD, Git, Databricks, PySpark, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9985441c9238ec</t>
+          <t>https://www.indeed.com/viewjob?jk=1d0c66ac5431d7f0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Freshfields</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, AKS, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Kubernetes, CI/CD, Databricks, Kafka, Hadoop, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9d12e8cbf2f5bba</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d212983a598443</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Architect</t>
+          <t>Python AI Full Stack</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, Kafka, MongoDB, Python, R, Java, Scala</t>
+          <t>Generative AI, RAG, Gemini, Copilot, Docker, Kubernetes, Jenkins, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c372fec6954adf93</t>
+          <t>https://www.indeed.com/viewjob?jk=6189f57aca0d755c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>SRE - DevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vestmark</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Prompt Engineering, PostgreSQL, MySQL, MongoDB, NoSQL, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Gemini, Kubernetes, CI/CD, Jenkins, Terraform, Git, Power BI, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c6a5e5cf5e67a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=c99c9c660d572e7c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Support Engineer (TeamCity)</t>
+          <t>Python AI Full Stack</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JetBrains</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Gemini, Copilot, Docker, Kubernetes, Jenkins, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5921dacde6ad5818</t>
+          <t>https://www.indeed.com/viewjob?jk=6d516411706cdcf2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Product Engineer, Associate</t>
+          <t>Python AI Full Stack</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pacific Gas and Electric</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Copilot, CI/CD, Terraform, Git, PostgreSQL, MySQL, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Gemini, Copilot, Docker, Kubernetes, Jenkins, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dacfdc0a247a93d</t>
+          <t>https://www.indeed.com/viewjob?jk=b0693f35639377dc</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pillsbury Winthrop Shaw Pittman</t>
+          <t>Plante Moran</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, MLflow, Databricks, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Databricks, PySpark, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e50e0275d56546</t>
+          <t>https://www.indeed.com/viewjob?jk=35a87a481b03a8f0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI and Software Solutions Architect (Remote, Contract)</t>
+          <t>Python AI Full Stack</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>INFUSE</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, Kafka, PostgreSQL, NoSQL, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Gemini, Copilot, Docker, Kubernetes, Jenkins, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1bfa1f3245af737</t>
+          <t>https://www.indeed.com/viewjob?jk=f05c7cf735acab34</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer III - ML Model Delivery</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Docker, Kubernetes, Terraform, Databricks, Python, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9623715fec95146</t>
+          <t>https://www.indeed.com/viewjob?jk=e2545e2fa204ae54</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Legal Solutions Architect</t>
+          <t>Data Software Engineer III</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Freshfields</t>
+          <t>Fetcherr</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Docker, AKS, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, BigQuery, Data Lake, CI/CD, BigQuery, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a78a626370aa6018</t>
+          <t>https://www.indeed.com/viewjob?jk=65602e609351d8b7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Consultant - Software Engineer</t>
+          <t>Senior Software Engineer (Big Data)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Torq Consulting</t>
+          <t>Bitsight</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+          <t>RAG, Copilot, Data Lake, Kubernetes, CI/CD, Git, Hadoop, Python, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87462cba5b348ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=f25be4d3379ce4fe</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Consultant - Software Engineer</t>
+          <t>Senior Product &amp; PLG Analyst (Full-Stack Data Scientist)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Torq Consulting</t>
+          <t>Nebius</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, BigQuery, Git, Snowflake, BigQuery, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,19 +1196,19 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbe099f28678d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=eb1f0f1cb29c8a0c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GRP Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1217,11 +1217,11 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b9fce73a2238a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=6d17e41966431127</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Sr. Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pillsbury Winthrop Shaw Pittman</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, MLflow, Databricks, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,94 +1266,94 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cd3548c5f4e148d</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7689efbfa17324</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>New College Grad - Industrial Engineer</t>
+          <t>Sr AI Engineer II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Manassas, VA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Git, Tableau, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edfb8807e4ec3a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=4a4c35ee630effff</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Universal Background Screening</t>
+          <t>CDS Logistics</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, MySQL, MongoDB, SQL, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, Git, Power BI, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1802ad0b463648dd</t>
+          <t>https://www.indeed.com/viewjob?jk=b37d3f365a2edc63</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, CI/CD, Terraform, Git, SQL, R, Java</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fea647a8765adb1b</t>
+          <t>https://www.indeed.com/viewjob?jk=6a2f12a24aa3d0f4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Enterprise Data Modeler</t>
+          <t>AI Software Technical Intern</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BOK Financial</t>
+          <t>Intel Corporation</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, PyTorch, Git, Python, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=699494cdcc6e8afe</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a52d91c5f2aba0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Contact Center</t>
+          <t>Junior Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Macy's</t>
+          <t>PolicyMe</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Johns Creek, GA, US USA</t>
+          <t>Ontario, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,157 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Kafka, Hadoop, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>LangChain, RAG, Prompt Engineering, Git, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=accfe7542b4f2229</t>
+          <t>https://www.indeed.com/viewjob?jk=368a8c55c48d0439</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Associate NLP / Machine Learning Scientist</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>RedBalloon LLC</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Moscow, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Hugging Face, Prompt Engineering, Sentence Transformers, PyTorch, MLflow, Docker, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7193cc10563ce1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Machine Learning and AI</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Givelify</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, R, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51c6626a19815c46</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Newark, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>BigQuery, CI/CD, Git, BigQuery, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d8335fc573067df</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa295c20686ad626</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-10-01.xlsx
+++ b/daily_matches/job_matches_2026-10-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS Lakehouse Data Engineer- GrantSolutions experienced only</t>
+          <t>Microservices Digital Software Engineer (Citi Retail Services)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Triwave Solutions Inc</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.7</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, Kinesis, Docker, CI/CD, Jenkins</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16509765dca147b7</t>
+          <t>https://www.indeed.com/viewjob?jk=5706dd6baebfde8f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Financial Services Technology Consulting, Financial Risk Technology (FRT) Engineering - Senior</t>
+          <t>Machine Learning Engineer, Predictive Maintenance</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>AssetWatch</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.3</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, S3, EC2, Data Lake, Docker, Kubernetes, AKS, CI/CD, Terraform</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, S3, Glue, Athena, Docker, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d4e445d09c33470</t>
+          <t>https://www.indeed.com/viewjob?jk=8a533bcbf8ae0b71</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Clinical Data Engineer</t>
+          <t>SPEC SOFTWARE DEVT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Murray, UT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.2</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Copilot, Redshift, BigQuery, Synapse, CI/CD, Git, Snowflake, Databricks, BigQuery, Redshift</t>
+          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Git, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17f0d739bf16af91</t>
+          <t>https://www.indeed.com/viewjob?jk=0443de525123e0a5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Shelton - Data Engineering - Engr- Data II</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Cortex, S3, Glue, Kinesis, CI/CD, Git, Snowflake, Databricks, PySpark</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ef615c91382283</t>
+          <t>https://www.indeed.com/viewjob?jk=e6429def610f5341</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Engineer (Data Scientist)</t>
+          <t>Senior Software Engineer: PDLC (Hybrid, Seattle)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zions Bancorporation</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, PyTorch, FastAPI, Docker, Kubernetes</t>
+          <t>RAG, Prompt Engineering, Redshift, BigQuery, Docker, Kubernetes, CI/CD, Git, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1815eb45aa2c108</t>
+          <t>https://www.indeed.com/viewjob?jk=3f9f4efced11f6d0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Architect - Associate</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Intermountain Health</t>
+          <t>Republic Services</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>West Valley City, UT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, CI/CD, Snowflake, Databricks, PySpark, Kafka, Tableau, Power BI, Python</t>
+          <t>RAG, S3, Glue, Athena, Data Lake, Kinesis, Git, Snowflake, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8052dec6a7c72b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=9b838b29c7c8ad8f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Scientist – ML / GenAI / LLM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Apache Airflow, CI/CD, GitHub Actions, Git, Snowflake, Databricks, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24dadced559e6fd5</t>
+          <t>https://www.indeed.com/viewjob?jk=f8fbceb239053e0f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (Python, Java, AWS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Synapse, CI/CD, Git, Snowflake, Databricks, Kafka, Power BI, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa0a61b0b1456bb</t>
+          <t>https://www.indeed.com/viewjob?jk=3a2c17b6e6619517</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Software Engineer, Data (L3)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, BigQuery, Dataflow, Apache Airflow, CI/CD, Databricks, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c87481ab8ef4260</t>
+          <t>https://www.indeed.com/viewjob?jk=102cee0c6adcda4e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Contract-To-Hire) (Remote)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NOV</t>
+          <t>RelMap Consulting</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Data Lake, CI/CD, Git, Databricks, PySpark, NoSQL, Python, SQL, R</t>
+          <t>RAG, Apache Airflow, CI/CD, GitHub Actions, Git, Snowflake, PostgreSQL, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d0c66ac5431d7f0</t>
+          <t>https://www.indeed.com/viewjob?jk=f168390c3d4033ba</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Analytics Data Engineer II - Homes.com - Arlington, VA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Databricks, Kafka, Hadoop, NoSQL, Python, SQL, R</t>
+          <t>RAG, Gemini, Copilot, Prompt Engineering, Git, Snowflake, Databricks, PySpark, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d212983a598443</t>
+          <t>https://www.indeed.com/viewjob?jk=196fad23ac814fb2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Python AI Full Stack</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Docker, Kubernetes, Jenkins, Terraform, Git, Python</t>
+          <t>Machine Learning Engineer, LangChain, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6189f57aca0d755c</t>
+          <t>https://www.indeed.com/viewjob?jk=3c4e4827f2acca3b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SRE - DevOps Engineer</t>
+          <t>ML Ops Engineer I</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Murphy USA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>El Dorado, AR, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Kubernetes, CI/CD, Jenkins, Terraform, Git, Power BI, Python</t>
+          <t>Data Scientist, MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c99c9c660d572e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=13256dd402d6bbc4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Python AI Full Stack</t>
+          <t>Research Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>University of Rochester</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Docker, Kubernetes, Jenkins, Terraform, Git, Python</t>
+          <t>Machine Learning Engineer, LangChain, LLaMA, Mistral, Hugging Face, TensorFlow, PyTorch, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d516411706cdcf2</t>
+          <t>https://www.indeed.com/viewjob?jk=1f5cb4b103250c30</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Python AI Full Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Promevo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Docker, Kubernetes, Jenkins, Terraform, Git, Python</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, BigQuery, Dataflow, Apache Airflow, Terraform, Git, BigQuery, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,42 +986,42 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0693f35639377dc</t>
+          <t>https://www.indeed.com/viewjob?jk=bf209f051368f0a6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>AI &amp; Machine Learning Engineering Consultant - Senior - Consulting - Location OPEN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Plante Moran</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Databricks, PySpark, Power BI, Python, SQL</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, PyTorch, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a87a481b03a8f0</t>
+          <t>https://www.indeed.com/viewjob?jk=fda4e8aa0e57c056</t>
         </is>
       </c>
     </row>
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f05c7cf735acab34</t>
+          <t>https://www.indeed.com/viewjob?jk=152caa53a179789b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Engineer, Platform Engineering - Systems</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Cboe Global Markets</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2545e2fa204ae54</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa3aad3d38521ef</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Software Engineer III</t>
+          <t>ETS Senior Engineer - Azure Databricks &amp; Data Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fetcherr</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Data Lake, CI/CD, BigQuery, Python, SQL, R, Scala</t>
+          <t>RAG, Synapse, Data Lake, AKS, CI/CD, Terraform, Git, Databricks, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65602e609351d8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=54993a3d0229e1bd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Big Data)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bitsight</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Data Lake, Kubernetes, CI/CD, Git, Hadoop, Python, R, Java</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f25be4d3379ce4fe</t>
+          <t>https://www.indeed.com/viewjob?jk=8d75297369fa64ca</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Product &amp; PLG Analyst (Full-Stack Data Scientist)</t>
+          <t>Senior Application Security Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nebius</t>
+          <t>Arrowstreet Capital LP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Git, Snowflake, BigQuery, Tableau, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb1f0f1cb29c8a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=e50557e995a6e35f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr. Data Algorithm Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, CI/CD, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d17e41966431127</t>
+          <t>https://www.indeed.com/viewjob?jk=f4bce3a0e5906809</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer</t>
+          <t>QA Analyst, Keeper App (Backend &amp; Platform)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>Keeper Security, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Power BI, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, MySQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7689efbfa17324</t>
+          <t>https://www.indeed.com/viewjob?jk=422b593c74d4ab8c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr AI Engineer II</t>
+          <t>Solar Performance Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Blue Sky Utility</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Copilot, PostgreSQL, Tableau, Power BI, Matplotlib, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a4c35ee630effff</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e05eaae5b874d1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer – Data and Platform Tools – Bloomberg Connects</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CDS Logistics</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, Git, Power BI, SQL, R, Scala</t>
+          <t>Generative AI, BigQuery, CI/CD, Jenkins, Terraform, BigQuery, Python, R, Java</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b37d3f365a2edc63</t>
+          <t>https://www.indeed.com/viewjob?jk=dee1f8a371bcc7ae</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Software Developer - AI &amp; Automation</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Carrollton, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, LLaMA, Prompt Engineering, Docker, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a2f12a24aa3d0f4</t>
+          <t>https://www.indeed.com/viewjob?jk=560c6c790e7e3c84</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Software Technical Intern</t>
+          <t>Software Developer - Full Stack (Work Management Software)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, PyTorch, Git, Python, R</t>
+          <t>Generative AI, RAG, Copilot, Kubernetes, Git, Kafka, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a52d91c5f2aba0</t>
+          <t>https://www.indeed.com/viewjob?jk=8a266f2528f7b3ec</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Junior Software Engineer (Remote)</t>
+          <t>GovCloud Distributed Systems Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PolicyMe</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ontario, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Git, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Copilot, Prompt Engineering, Docker, Kubernetes, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=368a8c55c48d0439</t>
+          <t>https://www.indeed.com/viewjob?jk=92fb50983b3ab68d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Associate NLP / Machine Learning Scientist</t>
+          <t>Analytics &amp; Data Consumption Co-op</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RedBalloon LLC</t>
+          <t>Novelis</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Moscow, ID, US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hugging Face, Prompt Engineering, Sentence Transformers, PyTorch, MLflow, Docker, Python, R, Optimization</t>
+          <t>Generative AI, RAG, Git, Databricks, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7193cc10563ce1e</t>
+          <t>https://www.indeed.com/viewjob?jk=0f9f708ada468818</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Machine Learning and AI</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Givelify</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, R, Scala, Optimization, A/B Testing</t>
+          <t>RAG, Synapse, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51c6626a19815c46</t>
+          <t>https://www.indeed.com/viewjob?jk=a0058b8ece0bab0e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>BigQuery, CI/CD, Git, BigQuery, Tableau, Python, SQL, R, Scala</t>
+          <t>RAG, Synapse, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d8335fc573067df</t>
+          <t>https://www.indeed.com/viewjob?jk=fce0252be99bd916</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+          <t>RAG, Synapse, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,147 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa295c20686ad626</t>
+          <t>https://www.indeed.com/viewjob?jk=d0afa695590a0c66</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Research Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Lafayette, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Generative AI, TensorFlow, PyTorch, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=753ea42432d2b549</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Tech Electronics Company</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Docker, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63ee2f61bbbf1448</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Data Scientist I</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CareSource</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Data Scientist, Snowflake, Databricks, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec87ebceace51a42</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Data Science(AI/ML)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Paramount Global US Inc</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Virginia, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82281625a5af4841</t>
         </is>
       </c>
     </row>
